--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,254 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123965725</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58136</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nylanda, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>482719</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6307822</v>
+      </c>
+      <c r="S3" t="n">
+        <v>200</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Öjaby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123965720</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58169</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nylanda, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>482719</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6307822</v>
+      </c>
+      <c r="S4" t="n">
+        <v>200</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Öjaby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123965725</v>
+        <v>123965720</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,20 +816,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965720</v>
+        <v>123965725</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>58136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,20 +940,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123965725</v>
+        <v>123965720</v>
       </c>
       <c r="B3" t="n">
-        <v>58158</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,20 +816,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123965720</v>
+        <v>123965725</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,20 +940,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1050,153 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124739936</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57727</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100124</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Backsvala</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Riparia riparia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nylanda södra, Öjaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>482853</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6307573</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Öjaby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Industriområde</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Madeleine Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Madeleine Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124739936</v>
+        <v>124982934</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482853</v>
+        <v>482780</v>
       </c>
       <c r="R5" t="n">
-        <v>6307573</v>
+        <v>6307743</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+          <t>Industriområde under utveckling med störa högar jord och grus.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1196,6 +1196,153 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124739936</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57727</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100124</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Backsvala</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Riparia riparia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nylanda södra, Öjaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>482853</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6307573</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Öjaby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Industriområde</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Madeleine Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Madeleine Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982934</v>
+        <v>124739936</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482780</v>
+        <v>482853</v>
       </c>
       <c r="R5" t="n">
-        <v>6307743</v>
+        <v>6307573</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
+          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med störa högar jord och grus.</t>
+          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124739936</v>
+        <v>124982934</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482853</v>
+        <v>482780</v>
       </c>
       <c r="R6" t="n">
-        <v>6307573</v>
+        <v>6307743</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1289,27 +1289,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+          <t>Industriområde under utveckling med störa högar jord och grus.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124739936</v>
+        <v>124982745</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+          <t>Industriområde under utveckling med stora högar av jord och grus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982745</v>
+        <v>124739936</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
+          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av jord och grus</t>
+          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,6 +1344,254 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125258622</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58218</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nylanda, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>482719</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6307822</v>
+      </c>
+      <c r="S7" t="n">
+        <v>200</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Öjaby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125258631</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56965</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nylanda, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>482719</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6307822</v>
+      </c>
+      <c r="S8" t="n">
+        <v>200</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Öjaby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Broman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982745</v>
+        <v>124739936</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
+          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av jord och grus</t>
+          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125258622</v>
+        <v>125258631</v>
       </c>
       <c r="B7" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,25 +1358,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125258631</v>
+        <v>125258622</v>
       </c>
       <c r="B8" t="n">
-        <v>56965</v>
+        <v>58218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124739936</v>
+        <v>124982745</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+          <t>Industriområde under utveckling med stora högar av jord och grus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125258631</v>
+        <v>125258622</v>
       </c>
       <c r="B7" t="n">
-        <v>56965</v>
+        <v>58218</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,25 +1358,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125258622</v>
+        <v>125258631</v>
       </c>
       <c r="B8" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982745</v>
+        <v>124982934</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482853</v>
+        <v>482780</v>
       </c>
       <c r="R5" t="n">
-        <v>6307573</v>
+        <v>6307743</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
+          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av jord och grus</t>
+          <t>Industriområde under utveckling med störa högar jord och grus.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124982934</v>
+        <v>124982745</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482780</v>
+        <v>482853</v>
       </c>
       <c r="R6" t="n">
-        <v>6307743</v>
+        <v>6307573</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
+          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med störa högar jord och grus.</t>
+          <t>Industriområde under utveckling med stora högar av jord och grus</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125258622</v>
+        <v>125258631</v>
       </c>
       <c r="B7" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,25 +1358,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125258631</v>
+        <v>125258622</v>
       </c>
       <c r="B8" t="n">
-        <v>56965</v>
+        <v>58218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982934</v>
+        <v>124982745</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482780</v>
+        <v>482853</v>
       </c>
       <c r="R5" t="n">
-        <v>6307743</v>
+        <v>6307573</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
+          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med störa högar jord och grus.</t>
+          <t>Industriområde under utveckling med stora högar av jord och grus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124982745</v>
+        <v>124982934</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482853</v>
+        <v>482780</v>
       </c>
       <c r="R6" t="n">
-        <v>6307573</v>
+        <v>6307743</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
+          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av jord och grus</t>
+          <t>Industriområde under utveckling med störa högar jord och grus.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125258631</v>
+        <v>125258622</v>
       </c>
       <c r="B7" t="n">
-        <v>56965</v>
+        <v>58218</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,25 +1358,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125258622</v>
+        <v>125258631</v>
       </c>
       <c r="B8" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982745</v>
+        <v>124739936</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
+          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av jord och grus</t>
+          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125258622</v>
+        <v>125258631</v>
       </c>
       <c r="B7" t="n">
-        <v>58218</v>
+        <v>56965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,25 +1358,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125258631</v>
+        <v>125258622</v>
       </c>
       <c r="B8" t="n">
-        <v>56965</v>
+        <v>58218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1591,6 +1591,135 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125454651</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57727</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100124</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backsvala</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Riparia riparia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nylanda söder, Öjaby, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>482754</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6307702</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Öjaby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många svalor runt bohålen i jordhögarna på södra delen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ola Bondesson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ola Bondesson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124739936</v>
+        <v>124982934</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57879</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482853</v>
+        <v>482780</v>
       </c>
       <c r="R5" t="n">
-        <v>6307573</v>
+        <v>6307743</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,27 +1142,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+          <t>Industriområde under utveckling med störa högar jord och grus.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124982934</v>
+        <v>124739936</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57879</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482780</v>
+        <v>482853</v>
       </c>
       <c r="R6" t="n">
-        <v>6307743</v>
+        <v>6307573</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1289,27 +1289,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
+          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med störa högar jord och grus.</t>
+          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125258631</v>
+        <v>125258622</v>
       </c>
       <c r="B7" t="n">
-        <v>56965</v>
+        <v>58345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,25 +1358,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125258622</v>
+        <v>125258631</v>
       </c>
       <c r="B8" t="n">
-        <v>58218</v>
+        <v>57053</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1597,7 +1597,7 @@
         <v>125454651</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57879</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982934</v>
+        <v>124982745</v>
       </c>
       <c r="B5" t="n">
         <v>57879</v>
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482780</v>
+        <v>482853</v>
       </c>
       <c r="R5" t="n">
-        <v>6307743</v>
+        <v>6307573</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
+          <t>En seriös entreprenör som har satt upp skyltar samt meddelat sina anställda att det är häckningsplats. Full aktivitet där de flyger in och ut ur bohålorna. Minst 25-30 bohålor i den "lilla högen".</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med störa högar jord och grus.</t>
+          <t>Industriområde under utveckling med stora högar av jord och grus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124739936</v>
+        <v>124982934</v>
       </c>
       <c r="B6" t="n">
         <v>57879</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482853</v>
+        <v>482780</v>
       </c>
       <c r="R6" t="n">
-        <v>6307573</v>
+        <v>6307743</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1289,27 +1289,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hade svårt att räkna antal individer då det var full aktivitet med backsvalor som konstant flög ut och in i bo-hålorna. 2024 konstaterades häckning vid samma grus/sandhög</t>
+          <t>Entreprenör är meddelad. Över 100 bohålor utspridda i 3 olika högar. I ngn hög fanns det bohålor på mer än en sida av jordhögen. Full aktivitet med fåglar som flög ut och in ur hålen i alla högarna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Industriområde under utveckling med stora högar av grus och sand.</t>
+          <t>Industriområde under utveckling med störa högar jord och grus.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125258622</v>
+        <v>125258631</v>
       </c>
       <c r="B7" t="n">
-        <v>58345</v>
+        <v>57053</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,25 +1358,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125258631</v>
+        <v>125258622</v>
       </c>
       <c r="B8" t="n">
-        <v>57053</v>
+        <v>58345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1057,11 +1057,6 @@
       <c r="B5" t="n">
         <v>57879</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1204,11 +1199,6 @@
       <c r="B6" t="n">
         <v>57879</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1349,12 +1339,7 @@
         <v>125258631</v>
       </c>
       <c r="B7" t="n">
-        <v>57053</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1473,12 +1458,7 @@
         <v>125258622</v>
       </c>
       <c r="B8" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,12 +1577,7 @@
         <v>125454651</v>
       </c>
       <c r="B9" t="n">
-        <v>57879</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1458,7 +1458,7 @@
         <v>125258622</v>
       </c>
       <c r="B8" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>125454651</v>
       </c>
       <c r="B9" t="n">
-        <v>57897</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2701-2020 artfynd.xlsx
+++ b/artfynd/A 2701-2020 artfynd.xlsx
@@ -1577,7 +1577,7 @@
         <v>125454651</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
